--- a/data/PLUGER.xlsx
+++ b/data/PLUGER.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ea4a19649b5fa823/Documentos/TRABAJO/MEGALO/SELLOUT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="302" documentId="8_{1FC06739-7DCE-4DD3-8436-12A82533DFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{647FC436-4228-4F22-B5DD-A772EC69A6D2}"/>
+  <xr:revisionPtr revIDLastSave="307" documentId="8_{1FC06739-7DCE-4DD3-8436-12A82533DFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C7738B7-66D0-4CC7-912B-F38EEAEBC6A9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{2E48FE94-A98C-4473-BAB0-81B310092486}"/>
   </bookViews>
@@ -806,14 +806,16 @@
       <c r="J3" s="11">
         <v>3200</v>
       </c>
-      <c r="K3" s="11"/>
+      <c r="K3" s="11">
+        <v>3500</v>
+      </c>
       <c r="L3" s="11"/>
       <c r="M3" s="11"/>
       <c r="N3" s="11"/>
       <c r="O3" s="11"/>
       <c r="P3" s="11">
         <f t="shared" ref="P3:P9" si="0">SUM(D3:O3)</f>
-        <v>21500</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
@@ -847,14 +849,16 @@
       <c r="J4" s="22">
         <v>1400</v>
       </c>
-      <c r="K4" s="22"/>
+      <c r="K4" s="22">
+        <v>700</v>
+      </c>
       <c r="L4" s="22"/>
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
       <c r="O4" s="22"/>
       <c r="P4" s="22">
         <f t="shared" si="0"/>
-        <v>8300</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -886,14 +890,16 @@
       <c r="J5" s="22">
         <v>700</v>
       </c>
-      <c r="K5" s="22"/>
+      <c r="K5" s="22">
+        <v>600</v>
+      </c>
       <c r="L5" s="22"/>
       <c r="M5" s="22"/>
       <c r="N5" s="22"/>
       <c r="O5" s="22"/>
       <c r="P5" s="22">
         <f t="shared" si="0"/>
-        <v>5600</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -927,14 +933,16 @@
       <c r="J6" s="22">
         <v>100</v>
       </c>
-      <c r="K6" s="22"/>
+      <c r="K6" s="22">
+        <v>200</v>
+      </c>
       <c r="L6" s="22"/>
       <c r="M6" s="22"/>
       <c r="N6" s="22"/>
       <c r="O6" s="22"/>
       <c r="P6" s="22">
         <f t="shared" si="0"/>
-        <v>4100</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
@@ -966,14 +974,16 @@
       <c r="J7" s="22">
         <v>100</v>
       </c>
-      <c r="K7" s="22"/>
+      <c r="K7" s="22">
+        <v>200</v>
+      </c>
       <c r="L7" s="22"/>
       <c r="M7" s="22"/>
       <c r="N7" s="22"/>
       <c r="O7" s="22"/>
       <c r="P7" s="22">
         <f t="shared" si="0"/>
-        <v>2900</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -1061,7 +1071,7 @@
       </c>
       <c r="K10" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="L10" s="7">
         <f t="shared" si="1"/>
@@ -1081,7 +1091,7 @@
       </c>
       <c r="P10" s="14">
         <f t="shared" si="1"/>
-        <v>42400</v>
+        <v>47600</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
